--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
@@ -133,18 +133,6 @@
     <t xml:space="preserve">San Gregorio</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
@@ -298,6 +286,12 @@
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">7107</t>
   </si>
   <si>
@@ -1291,6 +1285,12 @@
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4201</t>
   </si>
   <si>
@@ -2161,7 +2161,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:11</t>
+    <t xml:space="preserve">2026-09-09 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -3025,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>62.42</v>
+        <v>58.56</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>8</v>
@@ -3036,10 +3036,10 @@
         <v>2018</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>40</v>
@@ -3057,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>61.62</v>
+        <v>57.95</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>8</v>
@@ -3089,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>58.56</v>
+        <v>50.81</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>8</v>
@@ -3100,10 +3100,10 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>44</v>
@@ -3121,7 +3121,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>57.95</v>
+        <v>46.05</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>8</v>
@@ -3153,7 +3153,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>50.81</v>
+        <v>36.84</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>8</v>
@@ -3164,10 +3164,10 @@
         <v>2018</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>48</v>
@@ -3185,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46.05</v>
+        <v>22.15</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>8</v>
@@ -3196,28 +3196,28 @@
         <v>2018</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>36.84</v>
+        <v>185.6</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>8</v>
@@ -3228,28 +3228,28 @@
         <v>2018</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.15</v>
+        <v>185.09</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>8</v>
@@ -3263,25 +3263,25 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>185.6</v>
+        <v>177.38</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>8</v>
@@ -3292,28 +3292,28 @@
         <v>2018</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>185.09</v>
+        <v>176.17</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>8</v>
@@ -3327,25 +3327,25 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>177.38</v>
+        <v>166.9</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>65</v>
@@ -3368,16 +3368,16 @@
         <v>66</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>176.17</v>
+        <v>163.31</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>8</v>
@@ -3388,28 +3388,28 @@
         <v>2018</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>166.9</v>
+        <v>160.71</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>8</v>
@@ -3420,28 +3420,28 @@
         <v>2018</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>163.31</v>
+        <v>160.37</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>8</v>
@@ -3452,28 +3452,28 @@
         <v>2018</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>160.71</v>
+        <v>159.86</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>8</v>
@@ -3484,28 +3484,28 @@
         <v>2018</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>160.37</v>
+        <v>159.05</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>8</v>
@@ -3516,10 +3516,10 @@
         <v>2018</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3528,16 +3528,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>159.86</v>
+        <v>155.59</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>8</v>
@@ -3548,10 +3548,10 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3560,16 +3560,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>159.05</v>
+        <v>150.93</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>8</v>
@@ -3580,10 +3580,10 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3592,16 +3592,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>155.59</v>
+        <v>147.41</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>8</v>
@@ -3612,10 +3612,10 @@
         <v>2018</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3624,16 +3624,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>150.93</v>
+        <v>147.13</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>8</v>
@@ -3644,10 +3644,10 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3656,16 +3656,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>147.41</v>
+        <v>147.03</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>8</v>
@@ -3676,10 +3676,10 @@
         <v>2018</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3688,16 +3688,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>147.13</v>
+        <v>144.84</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>8</v>
@@ -3708,10 +3708,10 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3720,16 +3720,16 @@
         <v>90</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>147.03</v>
+        <v>144.73</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>8</v>
@@ -3740,10 +3740,10 @@
         <v>2018</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3752,16 +3752,16 @@
         <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>144.84</v>
+        <v>143.78</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3784,16 +3784,16 @@
         <v>94</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>143.78</v>
+        <v>138.58</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>8</v>
@@ -3804,10 +3804,10 @@
         <v>2018</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3816,16 +3816,16 @@
         <v>96</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>138.58</v>
+        <v>138.48</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>8</v>
@@ -3836,10 +3836,10 @@
         <v>2018</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3848,16 +3848,16 @@
         <v>98</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>138.48</v>
+        <v>138.04</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>8</v>
@@ -3868,10 +3868,10 @@
         <v>2018</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3880,16 +3880,16 @@
         <v>100</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>138.04</v>
+        <v>137.77</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>8</v>
@@ -3900,10 +3900,10 @@
         <v>2018</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3912,16 +3912,16 @@
         <v>102</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>137.77</v>
+        <v>134.7</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>8</v>
@@ -3935,7 +3935,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3944,16 +3944,16 @@
         <v>104</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>134.7</v>
+        <v>132.35</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>8</v>
@@ -3967,7 +3967,7 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3976,16 +3976,16 @@
         <v>106</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>132.35</v>
+        <v>126.76</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>8</v>
@@ -3996,10 +3996,10 @@
         <v>2018</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -4008,16 +4008,16 @@
         <v>108</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>126.76</v>
+        <v>125.7</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>8</v>
@@ -4028,10 +4028,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -4040,16 +4040,16 @@
         <v>110</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>125.7</v>
+        <v>125.35</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>8</v>
@@ -4060,10 +4060,10 @@
         <v>2018</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -4072,16 +4072,16 @@
         <v>112</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>125.35</v>
+        <v>125.34</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>8</v>
@@ -4092,10 +4092,10 @@
         <v>2018</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -4104,16 +4104,16 @@
         <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>125.34</v>
+        <v>125.33</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>8</v>
@@ -4124,10 +4124,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4136,16 +4136,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>125.33</v>
+        <v>125.26</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>8</v>
@@ -4156,10 +4156,10 @@
         <v>2018</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4168,16 +4168,16 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>125.26</v>
+        <v>124.87</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>8</v>
@@ -4188,10 +4188,10 @@
         <v>2018</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4200,16 +4200,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>124.87</v>
+        <v>123.52</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>8</v>
@@ -4220,10 +4220,10 @@
         <v>2018</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4232,16 +4232,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>123.52</v>
+        <v>122.64</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>8</v>
@@ -4252,10 +4252,10 @@
         <v>2018</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4264,16 +4264,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>122.64</v>
+        <v>122.53</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>8</v>
@@ -4284,10 +4284,10 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4296,16 +4296,16 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>122.53</v>
+        <v>121.19</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>8</v>
@@ -4316,10 +4316,10 @@
         <v>2018</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4328,16 +4328,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>121.19</v>
+        <v>121.04</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>8</v>
@@ -4348,10 +4348,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4360,16 +4360,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>121.04</v>
+        <v>120.7</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>8</v>
@@ -4383,7 +4383,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4392,16 +4392,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>120.7</v>
+        <v>120.54</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>8</v>
@@ -4412,10 +4412,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4424,16 +4424,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>120.54</v>
+        <v>120.12</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>8</v>
@@ -4444,10 +4444,10 @@
         <v>2018</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4456,16 +4456,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>120.12</v>
+        <v>119.11</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>8</v>
@@ -4476,10 +4476,10 @@
         <v>2018</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4488,16 +4488,16 @@
         <v>138</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>119.11</v>
+        <v>118.35</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>8</v>
@@ -4508,10 +4508,10 @@
         <v>2018</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4520,16 +4520,16 @@
         <v>140</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>118.35</v>
+        <v>117.82</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>8</v>
@@ -4540,10 +4540,10 @@
         <v>2018</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4552,16 +4552,16 @@
         <v>142</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>117.82</v>
+        <v>117.64</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>8</v>
@@ -4572,10 +4572,10 @@
         <v>2018</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4584,16 +4584,16 @@
         <v>144</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>117.64</v>
+        <v>116.84</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>8</v>
@@ -4604,10 +4604,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4616,16 +4616,16 @@
         <v>146</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>116.84</v>
+        <v>116.83</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>8</v>
@@ -4636,10 +4636,10 @@
         <v>2018</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4648,16 +4648,16 @@
         <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>116.83</v>
+        <v>116.79</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>8</v>
@@ -4671,7 +4671,7 @@
         <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -4680,16 +4680,16 @@
         <v>150</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>116.79</v>
+        <v>116.71</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>8</v>
@@ -4703,7 +4703,7 @@
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4712,16 +4712,16 @@
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>116.71</v>
+        <v>116.7</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>8</v>
@@ -4732,10 +4732,10 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4744,16 +4744,16 @@
         <v>154</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>116.7</v>
+        <v>116.33</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>8</v>
@@ -4767,7 +4767,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4776,16 +4776,16 @@
         <v>156</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>116.33</v>
+        <v>116.25</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>8</v>
@@ -4796,10 +4796,10 @@
         <v>2018</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4808,16 +4808,16 @@
         <v>158</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>116.25</v>
+        <v>115.08</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>8</v>
@@ -4828,10 +4828,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4840,16 +4840,16 @@
         <v>160</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>115.08</v>
+        <v>114.97</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>8</v>
@@ -4863,7 +4863,7 @@
         <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4872,16 +4872,16 @@
         <v>162</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>114.97</v>
+        <v>114.84</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>8</v>
@@ -4892,10 +4892,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4904,16 +4904,16 @@
         <v>164</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>114.84</v>
+        <v>114.6</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>8</v>
@@ -4924,10 +4924,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4936,16 +4936,16 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>114.6</v>
+        <v>114.46</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>8</v>
@@ -4956,10 +4956,10 @@
         <v>2018</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4968,16 +4968,16 @@
         <v>168</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>114.46</v>
+        <v>113.32</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>8</v>
@@ -4988,10 +4988,10 @@
         <v>2018</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -5000,16 +5000,16 @@
         <v>170</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>113.32</v>
+        <v>112.94</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -5032,16 +5032,16 @@
         <v>172</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>112.94</v>
+        <v>111.24</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>8</v>
@@ -5052,10 +5052,10 @@
         <v>2018</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5064,16 +5064,16 @@
         <v>174</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>111.24</v>
+        <v>110.52</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>8</v>
@@ -5084,10 +5084,10 @@
         <v>2018</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5096,16 +5096,16 @@
         <v>176</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>110.52</v>
+        <v>110.39</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>8</v>
@@ -5116,10 +5116,10 @@
         <v>2018</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5128,16 +5128,16 @@
         <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>110.39</v>
+        <v>110.28</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>8</v>
@@ -5148,10 +5148,10 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5160,16 +5160,16 @@
         <v>180</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>110.28</v>
+        <v>110.01</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>8</v>
@@ -5180,10 +5180,10 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5192,16 +5192,16 @@
         <v>182</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>110.01</v>
+        <v>109.91</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>8</v>
@@ -5212,10 +5212,10 @@
         <v>2018</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5224,16 +5224,16 @@
         <v>184</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>109.91</v>
+        <v>109.28</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>8</v>
@@ -5244,10 +5244,10 @@
         <v>2018</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5256,16 +5256,16 @@
         <v>186</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>109.28</v>
+        <v>108.95</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>8</v>
@@ -5276,10 +5276,10 @@
         <v>2018</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>187</v>
@@ -5288,16 +5288,16 @@
         <v>188</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>108.95</v>
+        <v>108.68</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>8</v>
@@ -5311,7 +5311,7 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5320,16 +5320,16 @@
         <v>190</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>108.68</v>
+        <v>108.34</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>8</v>
@@ -5340,10 +5340,10 @@
         <v>2018</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5352,16 +5352,16 @@
         <v>192</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>108.34</v>
+        <v>108.32</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>8</v>
@@ -5372,10 +5372,10 @@
         <v>2018</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5384,16 +5384,16 @@
         <v>194</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>108.32</v>
+        <v>108.28</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>8</v>
@@ -5407,7 +5407,7 @@
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5416,16 +5416,16 @@
         <v>196</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>108.28</v>
+        <v>107.91</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5448,16 +5448,16 @@
         <v>198</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>107.91</v>
+        <v>107.21</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>8</v>
@@ -5468,10 +5468,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5480,16 +5480,16 @@
         <v>200</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>107.21</v>
+        <v>106.95</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>8</v>
@@ -5500,10 +5500,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5512,16 +5512,16 @@
         <v>202</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>106.95</v>
+        <v>106.69</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>8</v>
@@ -5532,10 +5532,10 @@
         <v>2018</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5544,16 +5544,16 @@
         <v>204</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>106.69</v>
+        <v>106.68</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>8</v>
@@ -5564,10 +5564,10 @@
         <v>2018</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5576,16 +5576,16 @@
         <v>206</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>106.68</v>
+        <v>106.63</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>8</v>
@@ -5596,10 +5596,10 @@
         <v>2018</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5608,16 +5608,16 @@
         <v>208</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>106.63</v>
+        <v>106.51</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>8</v>
@@ -5628,10 +5628,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5640,16 +5640,16 @@
         <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>106.51</v>
+        <v>106.18</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>8</v>
@@ -5660,10 +5660,10 @@
         <v>2018</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>211</v>
@@ -5672,16 +5672,16 @@
         <v>212</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>106.18</v>
+        <v>105.91</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>8</v>
@@ -5692,10 +5692,10 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5704,16 +5704,16 @@
         <v>214</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>105.91</v>
+        <v>105.62</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>8</v>
@@ -5724,10 +5724,10 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5736,16 +5736,16 @@
         <v>216</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>105.62</v>
+        <v>105.4</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>8</v>
@@ -5756,10 +5756,10 @@
         <v>2018</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5768,16 +5768,16 @@
         <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>105.4</v>
+        <v>105.13</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>8</v>
@@ -5788,10 +5788,10 @@
         <v>2018</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5800,16 +5800,16 @@
         <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>105.13</v>
+        <v>104.4</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>8</v>
@@ -5823,7 +5823,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5832,16 +5832,16 @@
         <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>104.4</v>
+        <v>104.24</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5864,16 +5864,16 @@
         <v>224</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>104.24</v>
+        <v>103.32</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>8</v>
@@ -5884,10 +5884,10 @@
         <v>2018</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5896,16 +5896,16 @@
         <v>226</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>103.32</v>
+        <v>102.97</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>8</v>
@@ -5916,10 +5916,10 @@
         <v>2018</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5928,16 +5928,16 @@
         <v>228</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>102.97</v>
+        <v>102.53</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>8</v>
@@ -5951,7 +5951,7 @@
         <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5960,16 +5960,16 @@
         <v>230</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>102.53</v>
+        <v>102.47</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>8</v>
@@ -5980,10 +5980,10 @@
         <v>2018</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5992,16 +5992,16 @@
         <v>232</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>102.47</v>
+        <v>102.45</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>8</v>
@@ -6012,10 +6012,10 @@
         <v>2018</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -6024,16 +6024,16 @@
         <v>234</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>102.45</v>
+        <v>101.23</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>8</v>
@@ -6044,10 +6044,10 @@
         <v>2018</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -6056,16 +6056,16 @@
         <v>236</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>101.23</v>
+        <v>101.05</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>8</v>
@@ -6076,10 +6076,10 @@
         <v>2018</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6088,16 +6088,16 @@
         <v>238</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>101.05</v>
+        <v>100.98</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>8</v>
@@ -6108,10 +6108,10 @@
         <v>2018</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6120,16 +6120,16 @@
         <v>240</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>100.98</v>
+        <v>100.52</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>8</v>
@@ -6140,10 +6140,10 @@
         <v>2018</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6152,16 +6152,16 @@
         <v>242</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>100.52</v>
+        <v>100.46</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>8</v>
@@ -6172,10 +6172,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6184,16 +6184,16 @@
         <v>244</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>100.46</v>
+        <v>99.97</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>8</v>
@@ -6204,10 +6204,10 @@
         <v>2018</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>245</v>
@@ -6216,16 +6216,16 @@
         <v>246</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>99.97</v>
+        <v>99.88</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>8</v>
@@ -6236,10 +6236,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6248,16 +6248,16 @@
         <v>248</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>99.88</v>
+        <v>99.81</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>8</v>
@@ -6268,10 +6268,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>249</v>
@@ -6280,16 +6280,16 @@
         <v>250</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>99.81</v>
+        <v>99.27</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>8</v>
@@ -6300,10 +6300,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6312,16 +6312,16 @@
         <v>252</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>99.27</v>
+        <v>99.21</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>8</v>
@@ -6332,10 +6332,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6344,16 +6344,16 @@
         <v>254</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>99.21</v>
+        <v>98.67</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>8</v>
@@ -6367,7 +6367,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6376,16 +6376,16 @@
         <v>256</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>98.67</v>
+        <v>98.57</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>8</v>
@@ -6396,10 +6396,10 @@
         <v>2018</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6408,16 +6408,16 @@
         <v>258</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>98.57</v>
+        <v>98.53</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>8</v>
@@ -6428,10 +6428,10 @@
         <v>2018</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6440,16 +6440,16 @@
         <v>260</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>98.53</v>
+        <v>97.38</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>8</v>
@@ -6460,10 +6460,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6472,16 +6472,16 @@
         <v>262</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>97.38</v>
+        <v>97.33</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>8</v>
@@ -6495,7 +6495,7 @@
         <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6504,16 +6504,16 @@
         <v>264</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>97.33</v>
+        <v>97.31</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>8</v>
@@ -6524,10 +6524,10 @@
         <v>2018</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6536,16 +6536,16 @@
         <v>266</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>97.31</v>
+        <v>97.03</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>8</v>
@@ -6559,7 +6559,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6568,16 +6568,16 @@
         <v>268</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>97.03</v>
+        <v>96.58</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>8</v>
@@ -6588,10 +6588,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6600,16 +6600,16 @@
         <v>270</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>96.58</v>
+        <v>96.29</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>8</v>
@@ -6623,7 +6623,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6632,16 +6632,16 @@
         <v>272</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>96.29</v>
+        <v>96.28</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>8</v>
@@ -6652,10 +6652,10 @@
         <v>2018</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6664,16 +6664,16 @@
         <v>274</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>96.28</v>
+        <v>96.25</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>8</v>
@@ -6684,10 +6684,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6696,16 +6696,16 @@
         <v>276</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>96.25</v>
+        <v>95.67</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>8</v>
@@ -6719,7 +6719,7 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6728,16 +6728,16 @@
         <v>278</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>95.67</v>
+        <v>95.5</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>8</v>
@@ -6751,7 +6751,7 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6760,16 +6760,16 @@
         <v>280</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>95.5</v>
+        <v>95.48</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>8</v>
@@ -6780,10 +6780,10 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6792,16 +6792,16 @@
         <v>282</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>95.48</v>
+        <v>95.01</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>8</v>
@@ -6812,10 +6812,10 @@
         <v>2018</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6824,16 +6824,16 @@
         <v>284</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>95.01</v>
+        <v>94.91</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>8</v>
@@ -6844,10 +6844,10 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6856,16 +6856,16 @@
         <v>286</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>94.91</v>
+        <v>94.58</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>8</v>
@@ -6876,10 +6876,10 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6888,16 +6888,16 @@
         <v>288</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>94.58</v>
+        <v>93.83</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>8</v>
@@ -6908,10 +6908,10 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6920,16 +6920,16 @@
         <v>290</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>93.83</v>
+        <v>93.79</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>8</v>
@@ -6940,10 +6940,10 @@
         <v>2018</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>291</v>
@@ -6952,16 +6952,16 @@
         <v>292</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>93.79</v>
+        <v>93.52</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>8</v>
@@ -6972,10 +6972,10 @@
         <v>2018</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6984,16 +6984,16 @@
         <v>294</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>93.52</v>
+        <v>93.06</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>8</v>
@@ -7004,10 +7004,10 @@
         <v>2018</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -7016,16 +7016,16 @@
         <v>296</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>93.06</v>
+        <v>93.01</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>8</v>
@@ -7039,7 +7039,7 @@
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -7048,10 +7048,10 @@
         <v>298</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>8</v>
@@ -7068,10 +7068,10 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7080,16 +7080,16 @@
         <v>300</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>93.01</v>
+        <v>92.97</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>8</v>
@@ -7100,10 +7100,10 @@
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7112,16 +7112,16 @@
         <v>302</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>92.97</v>
+        <v>92.91</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>8</v>
@@ -7135,7 +7135,7 @@
         <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7144,16 +7144,16 @@
         <v>304</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>92.91</v>
+        <v>92.14</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>8</v>
@@ -7164,10 +7164,10 @@
         <v>2018</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7176,10 +7176,10 @@
         <v>306</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>8</v>
@@ -7196,10 +7196,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7208,16 +7208,16 @@
         <v>308</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>92.14</v>
+        <v>92.09</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>8</v>
@@ -7228,10 +7228,10 @@
         <v>2018</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7240,16 +7240,16 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>92.09</v>
+        <v>91.86</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>8</v>
@@ -7260,10 +7260,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7272,16 +7272,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>91.86</v>
+        <v>91.35</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>8</v>
@@ -7292,10 +7292,10 @@
         <v>2018</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7304,16 +7304,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>91.35</v>
+        <v>89.68</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>8</v>
@@ -7324,10 +7324,10 @@
         <v>2018</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7336,16 +7336,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>89.68</v>
+        <v>88.62</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>8</v>
@@ -7356,10 +7356,10 @@
         <v>2018</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7368,16 +7368,16 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>88.62</v>
+        <v>87.93</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>8</v>
@@ -7388,10 +7388,10 @@
         <v>2018</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7400,16 +7400,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>87.93</v>
+        <v>87.91</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>8</v>
@@ -7420,10 +7420,10 @@
         <v>2018</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7432,16 +7432,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>87.91</v>
+        <v>87.88</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>8</v>
@@ -7452,10 +7452,10 @@
         <v>2018</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7464,16 +7464,16 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>87.88</v>
+        <v>87.63</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>8</v>
@@ -7484,10 +7484,10 @@
         <v>2018</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7496,16 +7496,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>87.63</v>
+        <v>85.77</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>8</v>
@@ -7516,10 +7516,10 @@
         <v>2018</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7528,16 +7528,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>85.77</v>
+        <v>85.5</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>8</v>
@@ -7548,10 +7548,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7560,16 +7560,16 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>85.5</v>
+        <v>84.75</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>8</v>
@@ -7580,10 +7580,10 @@
         <v>2018</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7592,16 +7592,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>84.75</v>
+        <v>84.58</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>8</v>
@@ -7612,10 +7612,10 @@
         <v>2018</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7624,16 +7624,16 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>84.58</v>
+        <v>83.81</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>8</v>
@@ -7644,10 +7644,10 @@
         <v>2018</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7656,16 +7656,16 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>83.81</v>
+        <v>83.54</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>8</v>
@@ -7676,10 +7676,10 @@
         <v>2018</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7688,16 +7688,16 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>83.54</v>
+        <v>83.28</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>8</v>
@@ -7708,10 +7708,10 @@
         <v>2018</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7720,16 +7720,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>83.28</v>
+        <v>82.1</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>8</v>
@@ -7740,10 +7740,10 @@
         <v>2018</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7752,16 +7752,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>82.1</v>
+        <v>82.09</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>8</v>
@@ -7772,10 +7772,10 @@
         <v>2018</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7784,16 +7784,16 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>82.09</v>
+        <v>80.73</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>8</v>
@@ -7804,10 +7804,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7816,16 +7816,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>80.73</v>
+        <v>80.03</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>8</v>
@@ -7836,10 +7836,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7848,16 +7848,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>80.03</v>
+        <v>78.93</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>8</v>
@@ -7868,10 +7868,10 @@
         <v>2018</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7880,16 +7880,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>78.93</v>
+        <v>78.71</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>8</v>
@@ -7900,10 +7900,10 @@
         <v>2018</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7912,16 +7912,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>78.71</v>
+        <v>77.81</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>8</v>
@@ -7932,10 +7932,10 @@
         <v>2018</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7944,16 +7944,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>77.81</v>
+        <v>77.69</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>8</v>
@@ -7967,7 +7967,7 @@
         <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7976,16 +7976,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>77.69</v>
+        <v>76.92</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>8</v>
@@ -7999,7 +7999,7 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -8008,16 +8008,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>76.92</v>
+        <v>75.99</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>8</v>
@@ -8031,7 +8031,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -8040,16 +8040,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>75.99</v>
+        <v>75.52</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>8</v>
@@ -8063,7 +8063,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8072,16 +8072,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>75.52</v>
+        <v>75.02</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>8</v>
@@ -8095,7 +8095,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8104,16 +8104,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>75.02</v>
+        <v>72.81</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>8</v>
@@ -8124,10 +8124,10 @@
         <v>2018</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8136,16 +8136,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>72.81</v>
+        <v>72.49</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>8</v>
@@ -8156,10 +8156,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8168,16 +8168,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>72.49</v>
+        <v>71.78</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>8</v>
@@ -8191,7 +8191,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8200,16 +8200,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>71.78</v>
+        <v>71.09</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>8</v>
@@ -8220,10 +8220,10 @@
         <v>2018</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8232,16 +8232,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>71.09</v>
+        <v>69.44</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>8</v>
@@ -8252,10 +8252,10 @@
         <v>2018</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8264,16 +8264,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>69.44</v>
+        <v>69.37</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>8</v>
@@ -8284,10 +8284,10 @@
         <v>2018</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8296,16 +8296,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>69.37</v>
+        <v>69.23</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>8</v>
@@ -8316,10 +8316,10 @@
         <v>2018</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8328,16 +8328,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>69.23</v>
+        <v>69.2</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8360,16 +8360,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>69.2</v>
+        <v>66.46</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>8</v>
@@ -8383,7 +8383,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8392,16 +8392,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>66.46</v>
+        <v>66.02</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>8</v>
@@ -8415,7 +8415,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8424,16 +8424,16 @@
         <v>384</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>66.02</v>
+        <v>63.26</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>8</v>
@@ -8447,7 +8447,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8456,16 +8456,16 @@
         <v>386</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>63.26</v>
+        <v>62.74</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>8</v>
@@ -8479,7 +8479,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>387</v>
@@ -8488,16 +8488,16 @@
         <v>388</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>62.74</v>
+        <v>58.82</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>8</v>
@@ -8511,7 +8511,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>389</v>
@@ -8520,16 +8520,16 @@
         <v>390</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>58.82</v>
+        <v>55.12</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>8</v>
@@ -8540,10 +8540,10 @@
         <v>2018</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>391</v>
@@ -8552,16 +8552,16 @@
         <v>392</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>55.12</v>
+        <v>53.99</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>8</v>
@@ -8572,10 +8572,10 @@
         <v>2018</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>393</v>
@@ -8584,16 +8584,16 @@
         <v>394</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>53.99</v>
+        <v>46.27</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>8</v>
@@ -8604,28 +8604,28 @@
         <v>2018</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>395</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>396</v>
+        <v>55</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>46.27</v>
+        <v>44.88</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>8</v>
@@ -8636,28 +8636,28 @@
         <v>2018</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E190" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F190" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>44.88</v>
+        <v>37.71</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>8</v>
@@ -8671,7 +8671,7 @@
         <v>13</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>398</v>
@@ -8680,16 +8680,16 @@
         <v>399</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>37.71</v>
+        <v>37.2</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>8</v>
@@ -8700,28 +8700,28 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>57</v>
+        <v>403</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>58</v>
+        <v>404</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>37.2</v>
+        <v>165.21</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>8</v>
@@ -8735,25 +8735,25 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E193" s="2" t="s">
+      <c r="G193" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="H193" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>165.21</v>
+        <v>147.09</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>407</v>
@@ -8776,16 +8776,16 @@
         <v>408</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>147.09</v>
+        <v>144.67</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>8</v>
@@ -8796,28 +8796,28 @@
         <v>2018</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>144.67</v>
+        <v>140.67</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>8</v>
@@ -8828,28 +8828,28 @@
         <v>2018</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>140.67</v>
+        <v>113.7</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>8</v>
@@ -8860,28 +8860,28 @@
         <v>2018</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>113.7</v>
+        <v>112.27</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>8</v>
@@ -8892,10 +8892,10 @@
         <v>2018</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>418</v>
@@ -8904,16 +8904,16 @@
         <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>112.27</v>
+        <v>108.68</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>8</v>
@@ -8924,10 +8924,10 @@
         <v>2018</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>420</v>
@@ -8936,16 +8936,16 @@
         <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>108.68</v>
+        <v>103.18</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>8</v>
@@ -8956,10 +8956,10 @@
         <v>2018</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>422</v>
@@ -8968,16 +8968,16 @@
         <v>423</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>103.18</v>
+        <v>102.91</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>8</v>
@@ -8991,7 +8991,7 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>424</v>
@@ -9000,10 +9000,10 @@
         <v>425</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>8</v>
@@ -9023,7 +9023,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>426</v>
@@ -9032,10 +9032,10 @@
         <v>427</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>8</v>
@@ -9055,7 +9055,7 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>428</v>
@@ -9064,10 +9064,10 @@
         <v>429</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>8</v>
@@ -9087,7 +9087,7 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>430</v>
@@ -9096,10 +9096,10 @@
         <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>8</v>
@@ -9119,7 +9119,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>432</v>
@@ -9128,10 +9128,10 @@
         <v>433</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>8</v>
@@ -9151,7 +9151,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>434</v>
@@ -9160,10 +9160,10 @@
         <v>435</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>436</v>
@@ -9192,10 +9192,10 @@
         <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>8</v>
@@ -9215,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>438</v>
@@ -9224,10 +9224,10 @@
         <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>8</v>
@@ -9247,7 +9247,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>440</v>
@@ -9256,10 +9256,10 @@
         <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>8</v>
@@ -9279,7 +9279,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>442</v>
@@ -9288,10 +9288,10 @@
         <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>8</v>
@@ -9311,7 +9311,7 @@
         <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9320,10 +9320,10 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>8</v>
@@ -9343,7 +9343,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9352,10 +9352,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>8</v>
@@ -9375,7 +9375,7 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9384,10 +9384,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>8</v>
@@ -9407,19 +9407,19 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>8</v>
@@ -9439,7 +9439,7 @@
         <v>15</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>451</v>
@@ -9448,10 +9448,10 @@
         <v>452</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>8</v>
@@ -9471,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>453</v>
@@ -9480,10 +9480,10 @@
         <v>454</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>8</v>
@@ -9503,7 +9503,7 @@
         <v>3</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>455</v>
@@ -9512,10 +9512,10 @@
         <v>456</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>8</v>
@@ -9544,10 +9544,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>8</v>
@@ -9576,10 +9576,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>15</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9608,10 +9608,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>8</v>
@@ -9631,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9640,10 +9640,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>8</v>
@@ -9663,7 +9663,7 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9672,10 +9672,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>8</v>
@@ -9695,7 +9695,7 @@
         <v>3</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9704,10 +9704,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>8</v>
@@ -9727,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
@@ -9736,10 +9736,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>8</v>
@@ -9768,10 +9768,10 @@
         <v>457</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>8</v>
@@ -9791,7 +9791,7 @@
         <v>3</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>473</v>
@@ -9800,10 +9800,10 @@
         <v>474</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>8</v>
@@ -9832,10 +9832,10 @@
         <v>476</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>8</v>
@@ -9864,10 +9864,10 @@
         <v>478</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>8</v>
@@ -9896,10 +9896,10 @@
         <v>480</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>8</v>
@@ -9919,7 +9919,7 @@
         <v>3</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>481</v>
@@ -9928,10 +9928,10 @@
         <v>482</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>8</v>
@@ -9960,10 +9960,10 @@
         <v>484</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>8</v>
@@ -9983,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D232" s="2" t="s">
         <v>485</v>
@@ -9992,10 +9992,10 @@
         <v>486</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>8</v>
@@ -10024,10 +10024,10 @@
         <v>488</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>8</v>
@@ -10056,10 +10056,10 @@
         <v>490</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>8</v>
@@ -10079,7 +10079,7 @@
         <v>1</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>491</v>
@@ -10088,10 +10088,10 @@
         <v>492</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>8</v>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15 15:33</t>
+    <t xml:space="preserve">2026-09-24 00:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_d_enveje_a_2018.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -67,7 +67,7 @@
     <t xml:space="preserve">D_ENVEJE_a</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11402</t>
@@ -145,9 +145,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
@@ -211,7 +208,7 @@
     <t xml:space="preserve">Paredones</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16202</t>
@@ -232,7 +229,7 @@
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5605</t>
@@ -265,7 +262,7 @@
     <t xml:space="preserve">16206</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">5602</t>
@@ -499,9 +496,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">13403</t>
   </si>
   <si>
@@ -1276,7 +1270,7 @@
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1403</t>
@@ -1510,7 +1504,7 @@
     <t xml:space="preserve">Alto Hospicio</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8308</t>
@@ -1576,7 +1570,7 @@
     <t xml:space="preserve">Quilleco</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9107</t>
@@ -1675,7 +1669,7 @@
     <t xml:space="preserve">Purranque</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14204</t>
@@ -2068,7 +2062,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">8102</t>
@@ -2134,7 +2128,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">8108</t>
@@ -2173,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:01</t>
+    <t xml:space="preserve">2026-10-05 17:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -3054,7 +3048,7 @@
         <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3083,10 +3077,10 @@
         <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3115,10 +3109,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3147,10 +3141,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -3179,10 +3173,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -3211,10 +3205,10 @@
         <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
@@ -3243,10 +3237,10 @@
         <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>13</v>
@@ -3272,19 +3266,19 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3304,19 +3298,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3336,19 +3330,19 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3368,19 +3362,19 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3400,19 +3394,19 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3432,19 +3426,19 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3464,19 +3458,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3496,19 +3490,19 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3528,19 +3522,19 @@
         <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3560,19 +3554,19 @@
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3592,19 +3586,19 @@
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3624,19 +3618,19 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3656,19 +3650,19 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3688,19 +3682,19 @@
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3720,19 +3714,19 @@
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3752,19 +3746,19 @@
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3784,19 +3778,19 @@
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3816,19 +3810,19 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3848,19 +3842,19 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3880,19 +3874,19 @@
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3912,19 +3906,19 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3944,19 +3938,19 @@
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3976,19 +3970,19 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -4008,19 +4002,19 @@
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -4040,19 +4034,19 @@
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4072,19 +4066,19 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4104,19 +4098,19 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4136,19 +4130,19 @@
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4168,19 +4162,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4200,19 +4194,19 @@
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4232,19 +4226,19 @@
         <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4264,19 +4258,19 @@
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4296,19 +4290,19 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4328,19 +4322,19 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4360,19 +4354,19 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4392,19 +4386,19 @@
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4424,19 +4418,19 @@
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4456,19 +4450,19 @@
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4488,19 +4482,19 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4520,19 +4514,19 @@
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4552,19 +4546,19 @@
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4584,19 +4578,19 @@
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4616,19 +4610,19 @@
         <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4648,19 +4642,19 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4680,19 +4674,19 @@
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4712,19 +4706,19 @@
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4744,19 +4738,19 @@
         <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4776,19 +4770,19 @@
         <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4808,19 +4802,19 @@
         <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4840,19 +4834,19 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4872,19 +4866,19 @@
         <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4904,19 +4898,19 @@
         <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4936,19 +4930,19 @@
         <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4968,19 +4962,19 @@
         <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -5000,19 +4994,19 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -5032,19 +5026,19 @@
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -5064,19 +5058,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5096,19 +5090,19 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5128,19 +5122,19 @@
         <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5160,19 +5154,19 @@
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5192,19 +5186,19 @@
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5224,19 +5218,19 @@
         <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5256,19 +5250,19 @@
         <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5288,19 +5282,19 @@
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5320,19 +5314,19 @@
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5352,19 +5346,19 @@
         <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5384,19 +5378,19 @@
         <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5416,19 +5410,19 @@
         <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5448,19 +5442,19 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5480,19 +5474,19 @@
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5512,19 +5506,19 @@
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5544,19 +5538,19 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5576,19 +5570,19 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5608,19 +5602,19 @@
         <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5640,19 +5634,19 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5672,19 +5666,19 @@
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5704,19 +5698,19 @@
         <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5736,19 +5730,19 @@
         <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5768,19 +5762,19 @@
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5800,19 +5794,19 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5832,19 +5826,19 @@
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5864,19 +5858,19 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5896,19 +5890,19 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5928,19 +5922,19 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5960,19 +5954,19 @@
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5992,19 +5986,19 @@
         <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -6024,19 +6018,19 @@
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -6056,19 +6050,19 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6088,19 +6082,19 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6120,19 +6114,19 @@
         <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6152,19 +6146,19 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6184,19 +6178,19 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6216,19 +6210,19 @@
         <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6248,19 +6242,19 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6280,19 +6274,19 @@
         <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6312,19 +6306,19 @@
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6344,19 +6338,19 @@
         <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6376,19 +6370,19 @@
         <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6408,19 +6402,19 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6440,19 +6434,19 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6472,19 +6466,19 @@
         <v>5</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6504,19 +6498,19 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6536,19 +6530,19 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6568,19 +6562,19 @@
         <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6600,19 +6594,19 @@
         <v>6</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6632,19 +6626,19 @@
         <v>6</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6664,19 +6658,19 @@
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6696,19 +6690,19 @@
         <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6728,19 +6722,19 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6760,19 +6754,19 @@
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6792,19 +6786,19 @@
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6824,19 +6818,19 @@
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6856,19 +6850,19 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6888,19 +6882,19 @@
         <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6920,19 +6914,19 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6952,19 +6946,19 @@
         <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6984,19 +6978,19 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -7016,19 +7010,19 @@
         <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -7048,19 +7042,19 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7080,19 +7074,19 @@
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7112,19 +7106,19 @@
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7144,19 +7138,19 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7176,19 +7170,19 @@
         <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7208,19 +7202,19 @@
         <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7240,19 +7234,19 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7272,19 +7266,19 @@
         <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7304,19 +7298,19 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7336,19 +7330,19 @@
         <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7368,19 +7362,19 @@
         <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7400,19 +7394,19 @@
         <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7432,19 +7426,19 @@
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7464,19 +7458,19 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7496,19 +7490,19 @@
         <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7528,19 +7522,19 @@
         <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7560,19 +7554,19 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7592,19 +7586,19 @@
         <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7624,19 +7618,19 @@
         <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7656,19 +7650,19 @@
         <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7688,19 +7682,19 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7720,19 +7714,19 @@
         <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7752,19 +7746,19 @@
         <v>5</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7784,19 +7778,19 @@
         <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7816,19 +7810,19 @@
         <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7848,19 +7842,19 @@
         <v>6</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7880,19 +7874,19 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7912,19 +7906,19 @@
         <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7944,19 +7938,19 @@
         <v>5</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7976,19 +7970,19 @@
         <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -8008,19 +8002,19 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -8040,19 +8034,19 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8072,19 +8066,19 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8104,19 +8098,19 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8136,19 +8130,19 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8168,19 +8162,19 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8200,19 +8194,19 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8232,19 +8226,19 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8264,19 +8258,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8296,19 +8290,19 @@
         <v>6</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8328,19 +8322,19 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8360,19 +8354,19 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8392,19 +8386,19 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8424,19 +8418,19 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8456,19 +8450,19 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8488,19 +8482,19 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8520,19 +8514,19 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8552,19 +8546,19 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8584,19 +8578,19 @@
         <v>13</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8616,19 +8610,19 @@
         <v>6</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8648,19 +8642,19 @@
         <v>13</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8680,19 +8674,19 @@
         <v>7</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8712,19 +8706,19 @@
         <v>13</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8744,19 +8738,19 @@
         <v>13</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8776,19 +8770,19 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="F194" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="G194" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8808,19 +8802,19 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8840,19 +8834,19 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8872,19 +8866,19 @@
         <v>15</v>
       </c>
       <c r="C197" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="F197" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8904,19 +8898,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="F198" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8936,19 +8930,19 @@
         <v>1</v>
       </c>
       <c r="C199" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="F199" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8968,19 +8962,19 @@
         <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -9000,19 +8994,19 @@
         <v>15</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -9032,19 +9026,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9064,19 +9058,19 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9096,19 +9090,19 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9128,19 +9122,19 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9160,19 +9154,19 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9192,19 +9186,19 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9224,19 +9218,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9256,19 +9250,19 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9288,19 +9282,19 @@
         <v>1</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9320,19 +9314,19 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9352,19 +9346,19 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9384,19 +9378,19 @@
         <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9416,19 +9410,19 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9448,19 +9442,19 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9480,19 +9474,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9512,19 +9506,19 @@
         <v>15</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9544,19 +9538,19 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9576,19 +9570,19 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9608,19 +9602,19 @@
         <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D220" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>463</v>
-      </c>
       <c r="F220" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9640,19 +9634,19 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9672,19 +9666,19 @@
         <v>15</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9704,19 +9698,19 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9736,19 +9730,19 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9768,19 +9762,19 @@
         <v>3</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9800,19 +9794,19 @@
         <v>1</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9832,19 +9826,19 @@
         <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9864,19 +9858,19 @@
         <v>3</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9896,19 +9890,19 @@
         <v>2</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9928,19 +9922,19 @@
         <v>2</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9960,19 +9954,19 @@
         <v>2</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9992,19 +9986,19 @@
         <v>3</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -10024,19 +10018,19 @@
         <v>2</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -10056,19 +10050,19 @@
         <v>1</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10088,19 +10082,19 @@
         <v>2</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10120,19 +10114,19 @@
         <v>2</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10152,19 +10146,19 @@
         <v>1</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10184,19 +10178,19 @@
         <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="F238" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E238" s="2" t="s">
+      <c r="G238" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10216,19 +10210,19 @@
         <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10248,19 +10242,19 @@
         <v>10</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10280,19 +10274,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10312,19 +10306,19 @@
         <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10344,19 +10338,19 @@
         <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10376,19 +10370,19 @@
         <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10408,19 +10402,19 @@
         <v>10</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10440,19 +10434,19 @@
         <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10472,19 +10466,19 @@
         <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="F247" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10504,19 +10498,19 @@
         <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10536,19 +10530,19 @@
         <v>10</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10568,19 +10562,19 @@
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10600,19 +10594,19 @@
         <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10632,19 +10626,19 @@
         <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10664,19 +10658,19 @@
         <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10696,19 +10690,19 @@
         <v>9</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10728,19 +10722,19 @@
         <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10760,19 +10754,19 @@
         <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10792,19 +10786,19 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10824,19 +10818,19 @@
         <v>9</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10856,19 +10850,19 @@
         <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10888,19 +10882,19 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10920,19 +10914,19 @@
         <v>8</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10952,19 +10946,19 @@
         <v>10</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10984,19 +10978,19 @@
         <v>14</v>
       </c>
       <c r="C263" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>554</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -11016,19 +11010,19 @@
         <v>10</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -11048,19 +11042,19 @@
         <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11080,19 +11074,19 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11112,19 +11106,19 @@
         <v>10</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11144,19 +11138,19 @@
         <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11176,19 +11170,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11208,19 +11202,19 @@
         <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11240,19 +11234,19 @@
         <v>9</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11272,19 +11266,19 @@
         <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11304,19 +11298,19 @@
         <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11336,19 +11330,19 @@
         <v>14</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11368,19 +11362,19 @@
         <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11400,19 +11394,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11432,19 +11426,19 @@
         <v>14</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11464,19 +11458,19 @@
         <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11496,19 +11490,19 @@
         <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11528,19 +11522,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11560,19 +11554,19 @@
         <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11592,19 +11586,19 @@
         <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11624,19 +11618,19 @@
         <v>14</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11656,19 +11650,19 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11688,19 +11682,19 @@
         <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11720,19 +11714,19 @@
         <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11752,19 +11746,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11784,19 +11778,19 @@
         <v>14</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11816,19 +11810,19 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11848,19 +11842,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11880,19 +11874,19 @@
         <v>10</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11912,19 +11906,19 @@
         <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11944,19 +11938,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11976,19 +11970,19 @@
         <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -12008,19 +12002,19 @@
         <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -12040,19 +12034,19 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12072,19 +12066,19 @@
         <v>14</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12104,19 +12098,19 @@
         <v>14</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12136,19 +12130,19 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12168,19 +12162,19 @@
         <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12200,19 +12194,19 @@
         <v>8</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12232,19 +12226,19 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12264,19 +12258,19 @@
         <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12296,19 +12290,19 @@
         <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12328,19 +12322,19 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12360,19 +12354,19 @@
         <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12392,19 +12386,19 @@
         <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12424,19 +12418,19 @@
         <v>14</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12456,19 +12450,19 @@
         <v>9</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12488,19 +12482,19 @@
         <v>8</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12520,19 +12514,19 @@
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12552,19 +12546,19 @@
         <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12584,19 +12578,19 @@
         <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12616,19 +12610,19 @@
         <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12648,19 +12642,19 @@
         <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12680,19 +12674,19 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12712,19 +12706,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12744,19 +12738,19 @@
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12776,19 +12770,19 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12808,19 +12802,19 @@
         <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12840,19 +12834,19 @@
         <v>9</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12872,19 +12866,19 @@
         <v>8</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12904,19 +12898,19 @@
         <v>8</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12936,19 +12930,19 @@
         <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12968,19 +12962,19 @@
         <v>14</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -13000,19 +12994,19 @@
         <v>9</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -13032,19 +13026,19 @@
         <v>9</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -13064,19 +13058,19 @@
         <v>8</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13096,19 +13090,19 @@
         <v>8</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13128,19 +13122,19 @@
         <v>10</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13160,19 +13154,19 @@
         <v>14</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13192,19 +13186,19 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13224,19 +13218,19 @@
         <v>8</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>15</v>
@@ -13256,19 +13250,19 @@
         <v>10</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>15</v>
@@ -13288,19 +13282,19 @@
         <v>10</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>15</v>
@@ -13320,19 +13314,19 @@
         <v>9</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>15</v>
@@ -13352,19 +13346,19 @@
         <v>9</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>15</v>
@@ -13384,19 +13378,19 @@
         <v>10</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>15</v>
@@ -13416,19 +13410,19 @@
         <v>8</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>15</v>
@@ -13448,19 +13442,19 @@
         <v>8</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>15</v>
@@ -13480,19 +13474,19 @@
         <v>8</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H341" s="2" t="s">
         <v>15</v>
@@ -13512,19 +13506,19 @@
         <v>10</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>15</v>
@@ -13544,19 +13538,19 @@
         <v>10</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H343" s="2" t="s">
         <v>15</v>
@@ -13576,19 +13570,19 @@
         <v>8</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>15</v>
@@ -13618,7 +13612,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13626,50 +13620,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -13691,16 +13685,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2">
@@ -13714,7 +13708,7 @@
         <v>2018</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
   </sheetData>
